--- a/data/trans_camb/IP1010-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; -0,3</t>
+          <t>-2,49; -0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; -0,3</t>
+          <t>-2,78; -0,31</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 6,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,0</t>
+          <t>-3,63; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 9,88</t>
+          <t>0,86; 10,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,32</t>
+          <t>-0,89; 2,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,19</t>
+          <t>0,46; 4,84</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,24</t>
+          <t>0,0; 7,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,24</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,57</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 4,09</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1577,17 +1577,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,86</t>
+          <t>-2,12; 0,86</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,0</t>
+          <t>-2,47; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,44</t>
+          <t>-0,88; 0,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,0</t>
+          <t>-2,43; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,58</t>
+          <t>-2,38; 0,32</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,0</t>
+          <t>-2,99; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,86</t>
+          <t>-1,96; 0,9</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,82; -0,2</t>
+          <t>-1,94; -0,2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,4</t>
+          <t>-1,6; 0,31</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,62</t>
+          <t>-0,27; 0,62</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,11</t>
+          <t>-0,48; 0,13</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,25</t>
+          <t>-0,93; 0,26</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,71</t>
+          <t>-0,69; 0,71</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,24</t>
+          <t>-0,41; 0,26</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,32</t>
+          <t>-0,45; 0,35</t>
         </is>
       </c>
     </row>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-89,99; 102,59</t>
+          <t>-89,54; 118,28</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-74,72; 261,99</t>
+          <t>-71,73; 224,48</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-78,87; 111,48</t>
+          <t>-72,93; 118,73</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-69,87; 167,94</t>
+          <t>-72,31; 149,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1010-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Provincia-trans_camb.xlsx
@@ -797,12 +797,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; -0,59</t>
+          <t>-4,84; -0,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; -0,59</t>
+          <t>-4,84; -0,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; -0,31</t>
+          <t>-2,51; -0,31</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,91</t>
+          <t>0,0; 4,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,63</t>
+          <t>0,0; 6,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,0</t>
+          <t>-5,1; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 10,13</t>
+          <t>0,86; 9,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,04</t>
+          <t>-0,86; 2,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,84</t>
+          <t>0,49; 5,36</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,1</t>
+          <t>0,0; 7,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,61</t>
+          <t>0,0; 3,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>0,0; 5,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,09</t>
+          <t>0,0; 4,02</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1577,17 +1577,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,86</t>
+          <t>-2,15; 0,86</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,0</t>
+          <t>-2,67; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,44</t>
+          <t>-1,09; 0,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,0</t>
+          <t>-2,64; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,32</t>
+          <t>-2,38; 0,35</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 0,0</t>
+          <t>-2,85; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,9</t>
+          <t>-1,96; 0,86</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,94; -0,2</t>
+          <t>-2,06; -0,2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,31</t>
+          <t>-1,4; 0,44</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,62</t>
+          <t>-0,28; 0,61</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,13</t>
+          <t>-0,5; 0,12</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,26</t>
+          <t>-0,92; 0,17</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,71</t>
+          <t>-0,62; 0,72</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,26</t>
+          <t>-0,5; 0,25</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,35</t>
+          <t>-0,41; 0,32</t>
         </is>
       </c>
     </row>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-89,54; 118,28</t>
+          <t>-88,19; 88,97</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-71,73; 224,48</t>
+          <t>-71,0; 220,36</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-72,93; 118,73</t>
+          <t>-79,6; 123,77</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-72,31; 149,18</t>
+          <t>-68,63; 145,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1010-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,8</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,8</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,8; -0,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,8; -0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; -0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; -0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; -0,3</t>
+          <t>-2,21; -0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; -0,31</t>
+          <t>-2,46; -0,3</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,49</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1,72</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,9</t>
+          <t>-4,33; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,79; 9,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,0</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,43</t>
+          <t>-0,88; 2,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,36</t>
+          <t>0,43; 5,19</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>527,1%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>527,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>1,35</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>0,0; 7,57</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,62; 0,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,22; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,44</t>
+          <t>-1,1; 0,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-19,98%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-19,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1690,17 +1690,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>-0,37</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-0,79</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-0,47</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,79</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,0</t>
+          <t>-2,63; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,35</t>
+          <t>-1,94; 0,86</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,0</t>
+          <t>-2,8; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,86</t>
+          <t>-2,01; 0,58</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,06; -0,2</t>
+          <t>-1,82; -0,2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,44</t>
+          <t>-1,48; 0,4</t>
         </is>
       </c>
     </row>
@@ -1766,17 +1766,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>-46,54%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-59,59%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-46,54%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,29</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>0,03</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>0,11</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-0,11</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,27 +1879,27 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,61</t>
+          <t>-0,93; 0,25</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,12</t>
+          <t>-0,64; 0,71</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,17</t>
+          <t>-0,26; 0,62</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,72</t>
+          <t>-0,46; 0,11</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,25</t>
+          <t>-0,52; 0,24</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-45,06%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>61,82%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-59,38%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-45,06%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,99; 102,59</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,72; 261,99</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-88,19; 88,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-71,0; 220,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-79,6; 123,77</t>
+          <t>-78,87; 111,48</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-68,63; 145,27</t>
+          <t>-69,87; 167,94</t>
         </is>
       </c>
     </row>
